--- a/verification/cases/roundtrip/comment_test/init.xlsx
+++ b/verification/cases/roundtrip/comment_test/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F265B70-3488-4397-9566-86A0245AB613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="19020" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,12 +25,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Shaun Kalley</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +54,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -72,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A2" authorId="0">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -96,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B2" authorId="0">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -120,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A3" authorId="0">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -144,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -168,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A4" authorId="0">
+    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -192,7 +198,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -216,7 +222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A5" authorId="0">
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -240,7 +246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -264,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -288,7 +294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -312,7 +318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A8" authorId="0">
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -336,7 +342,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -373,7 +379,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -472,6 +478,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -796,25 +810,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2"/>
-    <row r="2" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2"/>
-    <row r="4" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:2"/>
-    <row r="7" spans="1:2"/>
-    <row r="8" spans="1:2"/>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
